--- a/i_test/test_D3_coorte_con_caratterizzazione/med_diab.xlsx
+++ b/i_test/test_D3_coorte_con_caratterizzazione/med_diab.xlsx
@@ -15,9 +15,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -55,12 +52,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,11 +351,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
@@ -372,6 +365,16 @@
           <t>DATE</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Table_cdm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
